--- a/stories/arbres/ATOM-LAN.MOT.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Oscar est dans la cuisine. Maman pose un cabas. Dedans, il y a une poire. Une clémentine. Une écharpe. Un gant. Oscar touche la poire. Elle est lisse et froide. Maman dit : on nomme. On classe. Les fruits ensemble. Les habits ensemble. La poire, c'est un fruit. La clémentine, c'est un fruit. Oscar les met ensemble. L'écharpe, c'est un habit. Le gant, c'est un habit. Oscar les met ensemble. Maman dit : fruits, c'est une catégorie. Habits, c'est une catégorie. Oscar répète : catégorie. Il pose les fruits dans le saladier. Il pose les habits sur la chaise. Parce qu'il a classé, chaque chose a sa place. Plus tard, maman sort une prune. Et une chaussette. Oscar dit : prune, fruit. Chaussette, habit. Il les met dans la bonne catégorie. Maman sourit. Oscar sent le parfum de la clémentine.</t>
+          <t>Oscar est dans la cuisine. Maman pose un cabas. Dedans, il y a une poire. Une clémentine. Une écharpe. Un gant. Oscar touche la poire. Elle est lisse et froide. On nomme. On classe. Les fruits ensemble. Les habits ensemble. La poire, c'est un fruit. La clémentine, c'est un fruit. Oscar les met ensemble. L'écharpe, c'est un habit. Le gant, c'est un habit. Oscar les met ensemble. Fruits, c'est une catégorie. Habits, c'est une catégorie. Oscar répète : catégorie. Il pose les fruits dans le saladier. Il pose les habits sur la chaise. Parce qu'il a classé, chaque chose a sa place. Plus tard, maman sort une prune. Et une chaussette. Prune, fruit. Chaussette, habit. Il les met dans la bonne catégorie. Maman sourit. Oscar sent le parfum de la clémentine.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Oscar est dans la cuisine. Maman pose un cabas. Dedans, il y a une poire. Une clémentine. Une écharpe. Un gant. Oscar touche la poire. Elle est lisse et froide.
+maman|On nomme. On classe.
+narrateur|Les fruits ensemble. Les habits ensemble. La poire, c'est un fruit. La clémentine, c'est un fruit. Oscar les met ensemble. L'écharpe, c'est un habit. Le gant, c'est un habit. Oscar les met ensemble.
+maman|Fruits, c'est une catégorie. Habits, c'est une catégorie.
+narrateur|Oscar répète : catégorie. Il pose les fruits dans le saladier. Il pose les habits sur la chaise. Parce qu'il a classé, chaque chose a sa place. Plus tard, maman sort une prune. Et une chaussette.
+enfant-m|Prune, fruit. Chaussette, habit. Il les met dans la bonne catégorie. Maman sourit.
+narrateur|Oscar sent le parfum de la clémentine.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Oscar range poire et écharpe. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Oscar a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Oscar croque la clémentine. Maman plie l'écharpe.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Oscar sent le parfum de la clémentine.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Oscar range poire et écharpe. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Oscar a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Oscar croque la clémentine. Maman plie l'écharpe.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.MOT.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Oscar classe fruits et habits</t>
+          <t>Le cabas froid de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le cabas rentre encore froid de la rue. Raphaël sent la clémentine, nomme, classe fruits et habits, puis une prune arrive.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Oscar est dans la cuisine. Maman pose un cabas. Dedans, il y a une poire. Une clémentine. Une écharpe. Un gant. Oscar touche la poire. Elle est lisse et froide. On nomme. On classe. Les fruits ensemble. Les habits ensemble. La poire, c'est un fruit. La clémentine, c'est un fruit. Oscar les met ensemble. L'écharpe, c'est un habit. Le gant, c'est un habit. Oscar les met ensemble. Fruits, c'est une catégorie. Habits, c'est une catégorie. Oscar répète : catégorie. Il pose les fruits dans le saladier. Il pose les habits sur la chaise. Parce qu'il a classé, chaque chose a sa place. Plus tard, maman sort une prune. Et une chaussette. Prune, fruit. Chaussette, habit. Il les met dans la bonne catégorie. Maman sourit. Oscar sent le parfum de la clémentine.</t>
+          <t>Le cabas est encore froid, tout mouillé. Il sent la clémentine, fort. Des bottes gouttent dans l'entrée. Une écharpe jaune glisse d'une chaise. La pluie tapote encore le rebord. La cuisine est un peu sombre, un peu douce. Raphaël, tu sens ? C'est la clémentine. Oui, maman. Ça pique un peu le nez. Le cabas a tout mélangé. On va ranger. En ce moment, Raphaël ouvre le cabas. Le tissu est rêche sous les doigts. Dedans, il y a une poire. Une clémentine. Une écharpe. Un gant. La poire est lisse et froide. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Raphaël prend la poire. Poire. C'est un fruit. Mets-la dans le saladier. Raphaël pose la poire dans le saladier. Le saladier sonne, tout clair. Il prend la clémentine. La peau est granuleuse, un peu froide. Clémentine. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Raphaël met la clémentine avec la poire. Il ramasse l'écharpe jaune. Elle est longue et douce. Écharpe. C'est un habit. Oui. Pose-la sur la chaise. Raphaël pose l'écharpe sur la chaise. Il prend le gant. Le gant est encore un peu humide. Gant. C'est un habit. Les habits ensemble. C'est une catégorie. Raphaël pose le gant sur la chaise. Catégorie. Fruits. Habits. Bravo, Raphaël. Tu as nommé. Tu as classé. Tu as mis ensemble. C'est du bon travail. Plus tard, maman sort encore une prune. Et une chaussette. À toi. Prune, fruit. Chaussette, habit. Il met la prune dans le saladier. Il pose la chaussette sur la chaise. Tu as fini de ranger le cabas ? Oui, maman. Raphaël sent encore le parfum de la clémentine. Les bottes gouttent plus lentement.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,20 +1324,78 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Oscar est dans la cuisine. Maman pose un cabas. Dedans, il y a une poire. Une clémentine. Une écharpe. Un gant. Oscar touche la poire. Elle est lisse et froide.
-maman|On nomme. On classe.
-narrateur|Les fruits ensemble. Les habits ensemble. La poire, c'est un fruit. La clémentine, c'est un fruit. Oscar les met ensemble. L'écharpe, c'est un habit. Le gant, c'est un habit. Oscar les met ensemble.
-maman|Fruits, c'est une catégorie. Habits, c'est une catégorie.
-narrateur|Oscar répète : catégorie. Il pose les fruits dans le saladier. Il pose les habits sur la chaise. Parce qu'il a classé, chaque chose a sa place. Plus tard, maman sort une prune. Et une chaussette.
-enfant-m|Prune, fruit. Chaussette, habit. Il les met dans la bonne catégorie. Maman sourit.
-narrateur|Oscar sent le parfum de la clémentine.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>enfants_parc</t>
-        </is>
-      </c>
+          <t>narrateur|Le cabas est encore froid, tout mouillé.
+narrateur|Il sent la clémentine, fort.
+narrateur|Des bottes gouttent dans l'entrée.
+narrateur|Une écharpe jaune glisse d'une chaise.
+narrateur|La pluie tapote encore le rebord.
+narrateur|La cuisine est un peu sombre, un peu douce.
+maman|Raphaël, tu sens ?
+maman|C'est la clémentine.
+enfant-m|Oui, maman.
+enfant-m|Ça pique un peu le nez.
+maman|Le cabas a tout mélangé.
+maman|On va ranger.
+narrateur|En ce moment, Raphaël ouvre le cabas.
+narrateur|Le tissu est rêche sous les doigts.
+narrateur|Dedans, il y a une poire.
+narrateur|Une clémentine.
+narrateur|Une écharpe.
+narrateur|Un gant.
+enfant-m|La poire est lisse et froide.
+maman|On nomme.
+maman|On classe.
+maman|Les fruits ensemble.
+maman|Les habits ensemble.
+narrateur|Raphaël prend la poire.
+enfant-m|Poire.
+enfant-m|C'est un fruit.
+maman|Mets-la dans le saladier.
+narrateur|Raphaël pose la poire dans le saladier.
+narrateur|Le saladier sonne, tout clair.
+narrateur|Il prend la clémentine.
+narrateur|La peau est granuleuse, un peu froide.
+enfant-m|Clémentine.
+enfant-m|C'est un fruit aussi.
+maman|Les fruits ensemble.
+maman|C'est une catégorie.
+narrateur|Raphaël met la clémentine avec la poire.
+narrateur|Il ramasse l'écharpe jaune.
+narrateur|Elle est longue et douce.
+enfant-m|Écharpe.
+enfant-m|C'est un habit.
+maman|Oui.
+maman|Pose-la sur la chaise.
+narrateur|Raphaël pose l'écharpe sur la chaise.
+narrateur|Il prend le gant.
+narrateur|Le gant est encore un peu humide.
+enfant-m|Gant.
+enfant-m|C'est un habit.
+maman|Les habits ensemble.
+maman|C'est une catégorie.
+narrateur|Raphaël pose le gant sur la chaise.
+enfant-m|Catégorie.
+enfant-m|Fruits.
+enfant-m|Habits.
+maman|Bravo, Raphaël.
+maman|Tu as nommé.
+maman|Tu as classé.
+maman|Tu as mis ensemble.
+maman|C'est du bon travail.
+narrateur|Plus tard, maman sort encore une prune.
+narrateur|Et une chaussette.
+maman|À toi.
+enfant-m|Prune, fruit.
+enfant-m|Chaussette, habit.
+narrateur|Il met la prune dans le saladier.
+narrateur|Il pose la chaussette sur la chaise.
+maman|Tu as fini de ranger le cabas ?
+enfant-m|Oui, maman.
+narrateur|Raphaël sent encore le parfum de la clémentine.
+narrateur|Les bottes gouttent plus lentement.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1350,7 +1420,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Oscar range poire et écharpe. Que fait-il ?</t>
+          <t>Raphaël range poire et écharpe. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1576,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Oscar range poire et écharpe. Que fait-il ?</t>
+          <t>narrateur|Raphaël range poire et écharpe.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1605,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Oscar a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits.</t>
+          <t>Raphaël a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo. C'est du bon travail, Raphaël. La prune est avec les fruits ? Oui. La chaussette est avec les habits. Le saladier est plein, tout frais. La chaise a une petite pile douce.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1749,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Oscar a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits.</t>
+          <t>narrateur|Raphaël a nommé.
+narrateur|Il a classé.
+narrateur|Une catégorie pour les fruits.
+narrateur|Une catégorie pour les habits.
+maman|Tu as mis ensemble.
+maman|Bravo.
+maman|C'est du bon travail, Raphaël.
+maman|La prune est avec les fruits ?
+enfant-m|Oui.
+enfant-m|La chaussette est avec les habits.
+narrateur|Le saladier est plein, tout frais.
+narrateur|La chaise a une petite pile douce.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1788,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Oscar croque la clémentine. Maman plie l'écharpe.</t>
+          <t>Raphaël croque la clémentine. Le jus pique un peu la langue. C'est acide, un peu ? Oui. C'est bon. Maman plie l'écharpe jaune. Elle pose le gant près des bottes. Les habits sèchent ensemble. Les fruits sont dans le saladier. On garde la prune pour plus tard ? Oui, maman. La pluie ralentit sur le rebord. Le cabas est vide, enfin. Tu as classé, puis tu goûtes. J'aime la clémentine.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1924,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Oscar croque la clémentine. Maman plie l'écharpe.</t>
+          <t>narrateur|Raphaël croque la clémentine.
+narrateur|Le jus pique un peu la langue.
+maman|C'est acide, un peu ?
+enfant-m|Oui.
+enfant-m|C'est bon.
+narrateur|Maman plie l'écharpe jaune.
+narrateur|Elle pose le gant près des bottes.
+maman|Les habits sèchent ensemble.
+enfant-m|Les fruits sont dans le saladier.
+maman|On garde la prune pour plus tard ?
+enfant-m|Oui, maman.
+narrateur|La pluie ralentit sur le rebord.
+narrateur|Le cabas est vide, enfin.
+maman|Tu as classé, puis tu goûtes.
+enfant-m|J'aime la clémentine.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1966,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai nommé. J'ai classé. Bravo. Tu as fait du bon travail. Le cabas sèche près de la porte. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2106,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai nommé.
+enfant-m|J'ai classé.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le cabas sèche près de la porte.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2171,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le cabas est encore froid, tout mouillé. Il sent la clémentine, fort. Des bottes gouttent dans l'entrée. Une écharpe jaune glisse d'une chaise. La pluie tapote encore le rebord. La cuisine est un peu sombre, un peu douce. Raphaël, tu sens ? C'est la clémentine. Oui, maman. Ça pique un peu le nez. Le cabas a tout mélangé. On va ranger. En ce moment, Raphaël ouvre le cabas. Le tissu est rêche sous les doigts. Dedans, il y a une poire. Une clémentine. Une écharpe. Un gant. La poire est lisse et froide. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Raphaël prend la poire. Poire. C'est un fruit. Mets-la dans le saladier. Raphaël pose la poire dans le saladier. Le saladier sonne, tout clair. Il prend la clémentine. La peau est granuleuse, un peu froide. Clémentine. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Raphaël met la clémentine avec la poire. Il ramasse l'écharpe jaune. Elle est longue et douce. Écharpe. C'est un habit. Oui. Pose-la sur la chaise. Raphaël pose l'écharpe sur la chaise. Il prend le gant. Le gant est encore un peu humide. Gant. C'est un habit. Les habits ensemble. C'est une catégorie. Raphaël pose le gant sur la chaise. Catégorie. Fruits. Habits. Bravo, Raphaël. Tu as nommé. Tu as classé. Tu as mis ensemble. C'est du bon travail. Plus tard, maman sort encore une prune. Et une chaussette. À toi. Prune, fruit. Chaussette, habit. Il met la prune dans le saladier. Il pose la chaussette sur la chaise. Tu as fini de ranger le cabas ? Oui, maman. Raphaël sent encore le parfum de la clémentine. Les bottes gouttent plus lentement.</t>
+          <t>Le cabas est encore froid, tout mouillé. Il sent la clémentine, fort. Des bottes gouttent dans l'entrée. Une écharpe jaune glisse d'une chaise. La pluie tapote encore le rebord. La cuisine est un peu sombre, un peu douce. Raphaël, tu sens ? C'est la clémentine. Oui, maman. Ça pique un peu le nez. Le cabas a tout mélangé. On va ranger. En ce moment, Raphaël ouvre le cabas. Le tissu est rêche sous les doigts. Dedans, il y a une poire. Une clémentine. Une écharpe. Un gant. La poire est lisse et froide. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Raphaël prend la poire. Poire. C'est un fruit. Mets-la dans le saladier. Raphaël pose la poire dans le saladier. Le saladier sonne, tout clair. Il prend la clémentine. La peau est granuleuse, un peu froide. Clémentine. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Raphaël met la clémentine avec la poire. Il ramasse l'écharpe jaune. Elle est longue et douce. Écharpe. C'est un habit. Oui. Pose-la sur la chaise. Raphaël pose l'écharpe sur la chaise. Il prend le gant. Le gant est encore un peu humide. Gant. C'est un habit. Les habits ensemble. C'est une catégorie. Raphaël pose le gant sur la chaise. Catégorie. Fruits. Habits. Bravo, Raphaël. Tu as nommé. Tu as classé. Tu as mis ensemble. Plus tard, maman sort encore une prune. Et une chaussette. À toi. Prune, fruit. Chaussette, habit. Il met la prune dans le saladier. Il pose la chaussette sur la chaise. Tu as fini de ranger le cabas ? Oui, maman. Raphaël sent encore le parfum de la clémentine. Les bottes gouttent plus lentement.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Oscar est dans la cuisine. Maman pose un cabas. Dedans, il y a une poire. Une clémentine. Une écharpe. Un gant. Oscar touche la poire. Elle est lisse et froide. Maman dit : on nomme. On classe. Les fruits ensemble. Les habits ensemble. La poire, c'est un fruit. La clémentine, c'est un fruit. Oscar les met ensemble. L'écharpe, c'est un habit. Le gant, c'est un habit. Oscar les met ensemble. Maman dit : fruits, c'est une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt;. Habits, c'est une catégorie. Oscar répète : catégorie. Il pose les fruits dans le saladier. Il pose les habits sur la chaise. Parce qu'il a classé, chaque chose a sa place. Plus tard, maman sort une prune. Et une chaussette. Oscar dit : prune, fruit. Chaussette, habit. Il les met dans la bonne catégorie. Maman sourit. Oscar sent le parfum de la clémentine.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le cabas est encore froid, tout mouillé. Il sent la clémentine, fort. Des bottes gouttent dans l'entrée. Une écharpe jaune glisse d'une chaise. La pluie tapote encore le rebord. La cuisine est un peu sombre, un peu douce. Raphaël, tu sens ? C'est la clémentine. Oui, maman. Ça pique un peu le nez. Le cabas a tout mélangé. On va ranger. En ce moment, Raphaël ouvre le cabas. Le tissu est rêche sous les doigts. Dedans, il y a une poire. Une clémentine. Une écharpe. Un gant. La poire est lisse et froide. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Raphaël prend la poire. Poire. C'est un fruit. Mets-la dans le saladier. Raphaël pose la poire dans le saladier. Le saladier sonne, tout clair. Il prend la clémentine. La peau est granuleuse, un peu froide. Clémentine. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Raphaël met la clémentine avec la poire. Il ramasse l'écharpe jaune. Elle est longue et douce. Écharpe. C'est un habit. Oui. Pose-la sur la chaise. Raphaël pose l'écharpe sur la chaise. Il prend le gant. Le gant est encore un peu humide. Gant. C'est un habit. Les habits ensemble. C'est une catégorie. Raphaël pose le gant sur la chaise. Catégorie. Fruits. Habits. Bravo, Raphaël. Tu as nommé. Tu as classé. Tu as mis ensemble. Plus tard, maman sort encore une prune. Et une chaussette. À toi. Prune, fruit. Chaussette, habit. Il met la prune dans le saladier. Il pose la chaussette sur la chaise. Tu as fini de ranger le cabas ? Oui, maman. Raphaël sent encore le parfum de la clémentine. Les bottes gouttent plus lentement.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1381,7 +1381,6 @@
 maman|Tu as nommé.
 maman|Tu as classé.
 maman|Tu as mis ensemble.
-maman|C'est du bon travail.
 narrateur|Plus tard, maman sort encore une prune.
 narrateur|Et une chaussette.
 maman|À toi.
@@ -1395,7 +1394,6 @@
 narrateur|Les bottes gouttent plus lentement.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1425,7 +1423,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Oscar range poire et écharpe. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël range poire et écharpe. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1580,7 +1578,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1605,12 +1602,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo. C'est du bon travail, Raphaël. La prune est avec les fruits ? Oui. La chaussette est avec les habits. Le saladier est plein, tout frais. La chaise a une petite pile douce.</t>
+          <t>Raphaël a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo. La prune est avec les fruits ? Oui. La chaussette est avec les habits. Le saladier est plein, tout frais. La chaise a une petite pile douce.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Oscar a nommé. Il a classé. Une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt; pour les fruits. Une catégorie pour les habits.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo. La prune est avec les fruits ? Oui. La chaussette est avec les habits. Le saladier est plein, tout frais. La chaise a une petite pile douce.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1755,7 +1752,6 @@
 narrateur|Une catégorie pour les habits.
 maman|Tu as mis ensemble.
 maman|Bravo.
-maman|C'est du bon travail, Raphaël.
 maman|La prune est avec les fruits ?
 enfant-m|Oui.
 enfant-m|La chaussette est avec les habits.
@@ -1763,7 +1759,6 @@
 narrateur|La chaise a une petite pile douce.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1793,7 +1788,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Oscar croque la clémentine. Maman plie l'écharpe.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël croque la clémentine. Le jus pique un peu la langue. C'est acide, un peu ? Oui. C'est bon. Maman plie l'écharpe jaune. Elle pose le gant près des bottes. Les habits sèchent ensemble. Les fruits sont dans le saladier. On garde la prune pour plus tard ? Oui, maman. La pluie ralentit sur le rebord. Le cabas est vide, enfin. Tu as classé, puis tu goûtes. J'aime la clémentine.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1941,7 +1936,6 @@
 enfant-m|J'aime la clémentine.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1966,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai nommé. J'ai classé. Bravo. Tu as fait du bon travail. Le cabas sèche près de la porte. L'histoire est finie.</t>
+          <t>J'ai nommé. J'ai classé. Bravo. Le cabas sèche près de la porte.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai nommé. J'ai classé. Bravo. Le cabas sèche près de la porte.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2109,12 +2103,9 @@
           <t>enfant-m|J'ai nommé.
 enfant-m|J'ai classé.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le cabas sèche près de la porte.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le cabas sèche près de la porte.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2133,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2178,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-04.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Oscar, maman</t>
+          <t>Raphaël, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-04.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-04.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le cabas froid de Raphaël</t>
+          <t>Le cheval sous la poire</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine après la pluie, cabas mouillé, mandarine</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Le cabas rentre encore froid de la rue. Raphaël sent la clémentine, nomme, classe fruits et habits, puis une prune arrive.</t>
+          <t>Raphaël veut son cheval de bois pour lui faire sentir la mandarine. Le cheval est perdu sous le bazar du cabas. En sortant fruits et habits, il le trouve, et le mot aussi.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le cabas est encore froid, tout mouillé. Il sent la clémentine, fort. Des bottes gouttent dans l'entrée. Une écharpe jaune glisse d'une chaise. La pluie tapote encore le rebord. La cuisine est un peu sombre, un peu douce. Raphaël, tu sens ? C'est la clémentine. Oui, maman. Ça pique un peu le nez. Le cabas a tout mélangé. On va ranger. En ce moment, Raphaël ouvre le cabas. Le tissu est rêche sous les doigts. Dedans, il y a une poire. Une clémentine. Une écharpe. Un gant. La poire est lisse et froide. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Raphaël prend la poire. Poire. C'est un fruit. Mets-la dans le saladier. Raphaël pose la poire dans le saladier. Le saladier sonne, tout clair. Il prend la clémentine. La peau est granuleuse, un peu froide. Clémentine. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Raphaël met la clémentine avec la poire. Il ramasse l'écharpe jaune. Elle est longue et douce. Écharpe. C'est un habit. Oui. Pose-la sur la chaise. Raphaël pose l'écharpe sur la chaise. Il prend le gant. Le gant est encore un peu humide. Gant. C'est un habit. Les habits ensemble. C'est une catégorie. Raphaël pose le gant sur la chaise. Catégorie. Fruits. Habits. Bravo, Raphaël. Tu as nommé. Tu as classé. Tu as mis ensemble. Plus tard, maman sort encore une prune. Et une chaussette. À toi. Prune, fruit. Chaussette, habit. Il met la prune dans le saladier. Il pose la chaussette sur la chaise. Tu as fini de ranger le cabas ? Oui, maman. Raphaël sent encore le parfum de la clémentine. Les bottes gouttent plus lentement.</t>
+          <t>Le cabas laisse une flaque près du paillasson. Il sent la mandarine, fort. Des bottes gouttent dans l'entrée. Une écharpe jaune glisse d'une anse. La pluie tapote encore le rebord. Tu as senti, Raphaël ? Ça pique le nez. C'est la mandarine. Je veux mon cheval. Il va la sentir, lui aussi. Il était dans le cabas. En ce moment, Raphaël fouille le tissu. Le tissu est rêche, tout froid. Une poire roule, lisse. Un gant tombe, encore mouillé. Il n'est pas là. Où est mon cheval ? On ne le voit pas, sous tout ça. Raphaël sort la poire. Elle est froide, toute ronde. Poire. Elle va avec les ronds froids ? Dans le saladier. La poire sonne dans le saladier. Il sort la mandarine. La peau est granuleuse, un peu mouillée. Mandarine. Avec la poire. Le saladier sent déjà le fruit. Raphaël ramasse l'écharpe jaune. Elle est longue, toute douce, un peu humide. Écharpe. Elle va sécher où ? Sur la chaise. Un papier collé vient avec l'écharpe. Des lettres y sont, un peu délavées. C'est un mot. Tu le connais ? Pas encore. Raphaël prend le gant mouillé. Sous le gant, quelque chose de dur. Mon cheval ! Le petit cheval de bois est froid, luisant. Une oreille a une goutte dessus. Cheval. C'est le mot, aussi. Maman montre le papier délavé. Les lettres disent le même nom. Cheval. Je l'avais perdu. Il était sous le gant. Merci, Raphaël. Tu as sorti les ronds, et les doux. Raphaël pose le cheval près du saladier. Le bois touche la mandarine. Il la sent.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Le cabas est encore froid, tout mouillé. Il sent la clémentine, fort. Des bottes gouttent dans l'entrée. Une écharpe jaune glisse d'une chaise. La pluie tapote encore le rebord. La cuisine est un peu sombre, un peu douce. Raphaël, tu sens ? C'est la clémentine. Oui, maman. Ça pique un peu le nez. Le cabas a tout mélangé. On va ranger. En ce moment, Raphaël ouvre le cabas. Le tissu est rêche sous les doigts. Dedans, il y a une poire. Une clémentine. Une écharpe. Un gant. La poire est lisse et froide. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Raphaël prend la poire. Poire. C'est un fruit. Mets-la dans le saladier. Raphaël pose la poire dans le saladier. Le saladier sonne, tout clair. Il prend la clémentine. La peau est granuleuse, un peu froide. Clémentine. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Raphaël met la clémentine avec la poire. Il ramasse l'écharpe jaune. Elle est longue et douce. Écharpe. C'est un habit. Oui. Pose-la sur la chaise. Raphaël pose l'écharpe sur la chaise. Il prend le gant. Le gant est encore un peu humide. Gant. C'est un habit. Les habits ensemble. C'est une catégorie. Raphaël pose le gant sur la chaise. Catégorie. Fruits. Habits. Bravo, Raphaël. Tu as nommé. Tu as classé. Tu as mis ensemble. Plus tard, maman sort encore une prune. Et une chaussette. À toi. Prune, fruit. Chaussette, habit. Il met la prune dans le saladier. Il pose la chaussette sur la chaise. Tu as fini de ranger le cabas ? Oui, maman. Raphaël sent encore le parfum de la clémentine. Les bottes gouttent plus lentement.</t>
+          <t>Le cabas laisse une flaque près du paillasson. Il sent la mandarine, fort. Des bottes gouttent dans l'entrée. Une écharpe jaune glisse d'une anse. La pluie tapote encore le rebord. Tu as senti, Raphaël ? Ça pique le nez. C'est la mandarine. Je veux mon cheval. Il va la sentir, lui aussi. Il était dans le cabas. En ce moment, Raphaël fouille le tissu. Le tissu est rêche, tout froid. Une poire roule, lisse. Un gant tombe, encore mouillé. Il n'est pas là. Où est mon cheval ? On ne le voit pas, sous tout ça. Raphaël sort la poire. Elle est froide, toute ronde. Poire. Elle va avec les ronds froids ? Dans le saladier. La poire sonne dans le saladier. Il sort la mandarine. La peau est granuleuse, un peu mouillée. Mandarine. Avec la poire. Le saladier sent déjà le fruit. Raphaël ramasse l'écharpe jaune. Elle est longue, toute douce, un peu humide. Écharpe. Elle va sécher où ? Sur la chaise. Un papier collé vient avec l'écharpe. Des lettres y sont, un peu délavées. C'est un mot. Tu le connais ? Pas encore. Raphaël prend le gant mouillé. Sous le gant, quelque chose de dur. Mon cheval ! Le petit cheval de bois est froid, luisant. Une oreille a une goutte dessus. Cheval. C'est le mot, aussi. Maman montre le papier délavé. Les lettres disent le même nom. Cheval. Je l'avais perdu. Il était sous le gant. Merci, Raphaël. Tu as sorti les ronds, et les doux. Raphaël pose le cheval près du saladier. Le bois touche la mandarine. Il la sent.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,74 +1324,62 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le cabas est encore froid, tout mouillé.
-narrateur|Il sent la clémentine, fort.
+          <t>narrateur|Le cabas laisse une flaque près du paillasson.
+narrateur|Il sent la mandarine, fort.
 narrateur|Des bottes gouttent dans l'entrée.
-narrateur|Une écharpe jaune glisse d'une chaise.
+narrateur|Une écharpe jaune glisse d'une anse.
 narrateur|La pluie tapote encore le rebord.
-narrateur|La cuisine est un peu sombre, un peu douce.
-maman|Raphaël, tu sens ?
-maman|C'est la clémentine.
-enfant-m|Oui, maman.
-enfant-m|Ça pique un peu le nez.
-maman|Le cabas a tout mélangé.
-maman|On va ranger.
-narrateur|En ce moment, Raphaël ouvre le cabas.
-narrateur|Le tissu est rêche sous les doigts.
-narrateur|Dedans, il y a une poire.
-narrateur|Une clémentine.
-narrateur|Une écharpe.
-narrateur|Un gant.
-enfant-m|La poire est lisse et froide.
-maman|On nomme.
-maman|On classe.
-maman|Les fruits ensemble.
-maman|Les habits ensemble.
-narrateur|Raphaël prend la poire.
+maman|Tu as senti, Raphaël ?
+enfant-m|Ça pique le nez.
+maman|C'est la mandarine.
+enfant-m|Je veux mon cheval.
+enfant-m|Il va la sentir, lui aussi.
+maman|Il était dans le cabas.
+narrateur|En ce moment, Raphaël fouille le tissu.
+narrateur|Le tissu est rêche, tout froid.
+narrateur|Une poire roule, lisse.
+narrateur|Un gant tombe, encore mouillé.
+enfant-m|Il n'est pas là.
+enfant-m|Où est mon cheval ?
+maman|On ne le voit pas, sous tout ça.
+narrateur|Raphaël sort la poire.
+narrateur|Elle est froide, toute ronde.
 enfant-m|Poire.
-enfant-m|C'est un fruit.
-maman|Mets-la dans le saladier.
-narrateur|Raphaël pose la poire dans le saladier.
-narrateur|Le saladier sonne, tout clair.
-narrateur|Il prend la clémentine.
-narrateur|La peau est granuleuse, un peu froide.
-enfant-m|Clémentine.
-enfant-m|C'est un fruit aussi.
-maman|Les fruits ensemble.
-maman|C'est une catégorie.
-narrateur|Raphaël met la clémentine avec la poire.
-narrateur|Il ramasse l'écharpe jaune.
-narrateur|Elle est longue et douce.
+maman|Elle va avec les ronds froids ?
+enfant-m|Dans le saladier.
+narrateur|La poire sonne dans le saladier.
+narrateur|Il sort la mandarine.
+narrateur|La peau est granuleuse, un peu mouillée.
+enfant-m|Mandarine.
+enfant-m|Avec la poire.
+narrateur|Le saladier sent déjà le fruit.
+narrateur|Raphaël ramasse l'écharpe jaune.
+narrateur|Elle est longue, toute douce, un peu humide.
 enfant-m|Écharpe.
-enfant-m|C'est un habit.
-maman|Oui.
-maman|Pose-la sur la chaise.
-narrateur|Raphaël pose l'écharpe sur la chaise.
-narrateur|Il prend le gant.
-narrateur|Le gant est encore un peu humide.
-enfant-m|Gant.
-enfant-m|C'est un habit.
-maman|Les habits ensemble.
-maman|C'est une catégorie.
-narrateur|Raphaël pose le gant sur la chaise.
-enfant-m|Catégorie.
-enfant-m|Fruits.
-enfant-m|Habits.
-maman|Bravo, Raphaël.
-maman|Tu as nommé.
-maman|Tu as classé.
-maman|Tu as mis ensemble.
-narrateur|Plus tard, maman sort encore une prune.
-narrateur|Et une chaussette.
-maman|À toi.
-enfant-m|Prune, fruit.
-enfant-m|Chaussette, habit.
-narrateur|Il met la prune dans le saladier.
-narrateur|Il pose la chaussette sur la chaise.
-maman|Tu as fini de ranger le cabas ?
-enfant-m|Oui, maman.
-narrateur|Raphaël sent encore le parfum de la clémentine.
-narrateur|Les bottes gouttent plus lentement.</t>
+maman|Elle va sécher où ?
+enfant-m|Sur la chaise.
+narrateur|Un papier collé vient avec l'écharpe.
+narrateur|Des lettres y sont, un peu délavées.
+enfant-m|C'est un mot.
+maman|Tu le connais ?
+enfant-m|Pas encore.
+narrateur|Raphaël prend le gant mouillé.
+narrateur|Sous le gant, quelque chose de dur.
+enfant-m|Mon cheval !
+narrateur|Le petit cheval de bois est froid, luisant.
+narrateur|Une oreille a une goutte dessus.
+enfant-m|Cheval.
+maman|C'est le mot, aussi.
+narrateur|Maman montre le papier délavé.
+narrateur|Les lettres disent le même nom.
+enfant-m|Cheval.
+enfant-m|Je l'avais perdu.
+maman|Il était sous le gant.
+maman|Merci, Raphaël.
+maman|Tu as sorti les ronds, et les doux.
+narrateur|Raphaël pose le cheval près du saladier.
+narrateur|Le bois touche la mandarine.
+enfant-m|Il la sent.</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1406,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Raphaël range poire et écharpe. Que fait-il ?</t>
+          <t>Raphaël cherche le cheval. Que fait-il des fruits et des habits ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Raphaël range poire et écharpe. Que fait-il ?</t>
+          <t>Raphaël cherche le cheval. Que fait-il des fruits et des habits ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1438,7 +1426,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>classer | ensemble | ranger | catégorie</t>
+          <t>classer | ensemble | ranger | catégorie | le cheval | fruits</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1453,7 +1441,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Les fruits vont ensemble. Que fait Oscar ?</t>
+          <t>Les ronds vont au saladier. Les doux sur la chaise. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1502,7 +1490,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1574,8 +1562,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël range poire et écharpe.
-narrateur|Que fait-il ?</t>
+          <t>narrateur|Raphaël cherche le cheval.
+narrateur|Que fait-il des fruits et des habits ?</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1590,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo. La prune est avec les fruits ? Oui. La chaussette est avec les habits. Le saladier est plein, tout frais. La chaise a une petite pile douce.</t>
+          <t>Le cabas est presque vide, enfin. Une chaussette reste au fond, oubliée. Chaussette. Avec l'écharpe, sur la chaise ? Oui. La pile de la chaise est douce, un peu humide. Le saladier est plein, tout frais. Le cheval a trouvé la mandarine ? Il la sent. Et toi, tu as trouvé le mot. Cheval. Raphaël fait avancer le bois sur la table. Toc, toc, tout petit. Il va jusqu'à la poire ? Oui. La poire est un grand rocher, pour lui. La mandarine est un soleil.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo. La prune est avec les fruits ? Oui. La chaussette est avec les habits. Le saladier est plein, tout frais. La chaise a une petite pile douce.</t>
+          <t>Le cabas est presque vide, enfin. Une chaussette reste au fond, oubliée. Chaussette. Avec l'écharpe, sur la chaise ? Oui. La pile de la chaise est douce, un peu humide. Le saladier est plein, tout frais. Le cheval a trouvé la mandarine ? Il la sent. Et toi, tu as trouvé le mot. Cheval. Raphaël fait avancer le bois sur la table. Toc, toc, tout petit. Il va jusqu'à la poire ? Oui. La poire est un grand rocher, pour lui. La mandarine est un soleil.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1670,7 +1658,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1746,17 +1734,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a nommé.
-narrateur|Il a classé.
-narrateur|Une catégorie pour les fruits.
-narrateur|Une catégorie pour les habits.
-maman|Tu as mis ensemble.
-maman|Bravo.
-maman|La prune est avec les fruits ?
+          <t>narrateur|Le cabas est presque vide, enfin.
+narrateur|Une chaussette reste au fond, oubliée.
+enfant-m|Chaussette.
+maman|Avec l'écharpe, sur la chaise ?
 enfant-m|Oui.
-enfant-m|La chaussette est avec les habits.
+narrateur|La pile de la chaise est douce, un peu humide.
 narrateur|Le saladier est plein, tout frais.
-narrateur|La chaise a une petite pile douce.</t>
+maman|Le cheval a trouvé la mandarine ?
+enfant-m|Il la sent.
+maman|Et toi, tu as trouvé le mot.
+enfant-m|Cheval.
+narrateur|Raphaël fait avancer le bois sur la table.
+narrateur|Toc, toc, tout petit.
+maman|Il va jusqu'à la poire ?
+enfant-m|Oui.
+narrateur|La poire est un grand rocher, pour lui.
+narrateur|La mandarine est un soleil.</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1777,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Raphaël croque la clémentine. Le jus pique un peu la langue. C'est acide, un peu ? Oui. C'est bon. Maman plie l'écharpe jaune. Elle pose le gant près des bottes. Les habits sèchent ensemble. Les fruits sont dans le saladier. On garde la prune pour plus tard ? Oui, maman. La pluie ralentit sur le rebord. Le cabas est vide, enfin. Tu as classé, puis tu goûtes. J'aime la clémentine.</t>
+          <t>Maman épluche la mandarine. Le jus pique un peu les doigts. C'est acide, un peu ? Oui. C'est bon. Raphaël en pose un quartier près du cheval. Pour lui. Il est revenu. Toi aussi, tu as retrouvé le mot. La pluie ralentit sur le rebord. Le cabas sèche, enfin vide. On garde la poire pour plus tard ? Oui, maman.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Raphaël croque la clémentine. Le jus pique un peu la langue. C'est acide, un peu ? Oui. C'est bon. Maman plie l'écharpe jaune. Elle pose le gant près des bottes. Les habits sèchent ensemble. Les fruits sont dans le saladier. On garde la prune pour plus tard ? Oui, maman. La pluie ralentit sur le rebord. Le cabas est vide, enfin. Tu as classé, puis tu goûtes. J'aime la clémentine.</t>
+          <t>Maman épluche la mandarine. Le jus pique un peu les doigts. C'est acide, un peu ? Oui. C'est bon. Raphaël en pose un quartier près du cheval. Pour lui. Il est revenu. Toi aussi, tu as retrouvé le mot. La pluie ralentit sur le rebord. Le cabas sèche, enfin vide. On garde la poire pour plus tard ? Oui, maman.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1851,7 +1845,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1919,21 +1913,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël croque la clémentine.
-narrateur|Le jus pique un peu la langue.
+          <t>narrateur|Maman épluche la mandarine.
+narrateur|Le jus pique un peu les doigts.
 maman|C'est acide, un peu ?
 enfant-m|Oui.
 enfant-m|C'est bon.
-narrateur|Maman plie l'écharpe jaune.
-narrateur|Elle pose le gant près des bottes.
-maman|Les habits sèchent ensemble.
-enfant-m|Les fruits sont dans le saladier.
-maman|On garde la prune pour plus tard ?
-enfant-m|Oui, maman.
+narrateur|Raphaël en pose un quartier près du cheval.
+enfant-m|Pour lui.
+maman|Il est revenu.
+maman|Toi aussi, tu as retrouvé le mot.
 narrateur|La pluie ralentit sur le rebord.
-narrateur|Le cabas est vide, enfin.
-maman|Tu as classé, puis tu goûtes.
-enfant-m|J'aime la clémentine.</t>
+narrateur|Le cabas sèche, enfin vide.
+maman|On garde la poire pour plus tard ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
     </row>
@@ -1960,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai nommé. J'ai classé. Bravo. Le cabas sèche près de la porte.</t>
+          <t>Le cheval de bois sent la mandarine. Je l'ai retrouvé. Oui. Le mot sèche près de l'écharpe. Le cabas ne cache plus rien.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai nommé. J'ai classé. Bravo. Le cabas sèche près de la porte.</t>
+          <t>Le cheval de bois sent la mandarine. Je l'ai retrouvé. Oui. Le mot sèche près de l'écharpe. Le cabas ne cache plus rien.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2021,14 +2013,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2100,10 +2092,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'ai nommé.
-enfant-m|J'ai classé.
-maman|Bravo.
-narrateur|Le cabas sèche près de la porte.</t>
+          <t>narrateur|Le cheval de bois sent la mandarine.
+enfant-m|Je l'ai retrouvé.
+maman|Oui.
+narrateur|Le mot sèche près de l'écharpe.
+narrateur|Le cabas ne cache plus rien.</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2174,6 +2167,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
